--- a/data/trans_dic/P02E$nadie-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P02E$nadie-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa</t>
+          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72,65; 87,21</t>
+          <t>72,51; 87,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,45; 91,5</t>
+          <t>78,87; 91,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,47; 92,14</t>
+          <t>78,42; 92,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79,07; 92,15</t>
+          <t>79,9; 92,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,83; 93,58</t>
+          <t>83,57; 93,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,63; 89,65</t>
+          <t>77,02; 89,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,57; 88,48</t>
+          <t>78,89; 88,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>83,57; 91,25</t>
+          <t>83,6; 91,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79,22; 88,71</t>
+          <t>79,6; 89,0</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,1; 93,12</t>
+          <t>75,17; 93,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,4; 95,55</t>
+          <t>85,17; 95,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,03; 94,5</t>
+          <t>83,49; 94,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87,82; 96,33</t>
+          <t>87,54; 96,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,14; 96,39</t>
+          <t>89,24; 96,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,1; 89,15</t>
+          <t>75,97; 88,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,28; 93,94</t>
+          <t>85,1; 93,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>89,35; 95,25</t>
+          <t>88,92; 95,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81,0; 89,95</t>
+          <t>81,0; 89,91</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86,39; 96,05</t>
+          <t>86,7; 95,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,79; 92,96</t>
+          <t>84,6; 93,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,83; 97,32</t>
+          <t>88,81; 97,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77,55; 93,78</t>
+          <t>77,84; 94,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>81,99; 94,77</t>
+          <t>81,73; 94,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,3; 100,0</t>
+          <t>89,09; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,69; 93,8</t>
+          <t>85,56; 94,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85,51; 92,55</t>
+          <t>85,53; 92,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90,55; 97,35</t>
+          <t>91,36; 97,42</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87,49; 94,91</t>
+          <t>87,7; 94,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90,28; 95,92</t>
+          <t>90,91; 95,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,47; 95,95</t>
+          <t>90,15; 96,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,01; 93,27</t>
+          <t>84,96; 93,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,79; 95,08</t>
+          <t>89,57; 94,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,68; 89,74</t>
+          <t>81,41; 89,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,87; 93,21</t>
+          <t>87,44; 93,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,08; 94,72</t>
+          <t>90,86; 94,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,3; 91,6</t>
+          <t>86,66; 91,74</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,69; 98,44</t>
+          <t>86,49; 98,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88,54; 97,58</t>
+          <t>88,97; 97,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,17; 94,97</t>
+          <t>84,76; 94,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90,07; 96,86</t>
+          <t>89,95; 97,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,13; 92,75</t>
+          <t>86,19; 92,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,76; 93,13</t>
+          <t>84,86; 93,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,98; 96,79</t>
+          <t>90,74; 96,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>88,17; 93,35</t>
+          <t>87,96; 93,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>86,47; 92,75</t>
+          <t>86,35; 92,53</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>81,26; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42,82; 100,0</t>
+          <t>50,23; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59,47; 95,07</t>
+          <t>59,97; 95,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>90,97; 96,91</t>
+          <t>90,71; 96,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>89,94; 96,14</t>
+          <t>90,02; 95,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>88,04; 95,85</t>
+          <t>87,47; 95,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>91,23; 97,02</t>
+          <t>91,45; 97,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>89,93; 95,76</t>
+          <t>89,85; 95,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87,18; 95,15</t>
+          <t>86,68; 94,9</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>87,2; 92,21</t>
+          <t>86,69; 91,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>89,52; 93,02</t>
+          <t>89,42; 93,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89,21; 93,24</t>
+          <t>89,14; 93,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89,77; 93,31</t>
+          <t>89,69; 93,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,12; 93,02</t>
+          <t>89,88; 93,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,46; 89,62</t>
+          <t>85,53; 89,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,45; 92,36</t>
+          <t>89,37; 92,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>90,41; 92,65</t>
+          <t>90,36; 92,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>87,78; 90,61</t>
+          <t>87,62; 90,5</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa</t>
+          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>82882; 99490</t>
+          <t>82714; 99535</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>119833; 138008</t>
+          <t>118961; 137464</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75038; 89241</t>
+          <t>75953; 89594</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>83953; 97834</t>
+          <t>84828; 98510</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>135582; 153193</t>
+          <t>136805; 152785</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>109442; 128033</t>
+          <t>110008; 127387</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>173055; 194874</t>
+          <t>173759; 194853</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>262845; 287022</t>
+          <t>262946; 287451</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>189871; 212615</t>
+          <t>190792; 213324</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64001; 79352</t>
+          <t>64062; 79948</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>131947; 147638</t>
+          <t>131593; 147720</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88972; 101262</t>
+          <t>89466; 101479</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125327; 137461</t>
+          <t>124922; 137508</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>176438; 190778</t>
+          <t>176639; 191085</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>121317; 140281</t>
+          <t>119543; 139664</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>194378; 214103</t>
+          <t>193957; 213766</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>314910; 335695</t>
+          <t>313399; 335368</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>214265; 237932</t>
+          <t>214266; 237821</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>104229; 115887</t>
+          <t>104607; 115495</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>164839; 180724</t>
+          <t>164455; 181109</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>124383; 136275</t>
+          <t>124362; 136049</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52250; 63187</t>
+          <t>52445; 63354</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>89682; 103670</t>
+          <t>89404; 103433</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48573; 54394</t>
+          <t>48458; 54394</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>161125; 176369</t>
+          <t>160884; 177197</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>259761; 281153</t>
+          <t>259832; 281060</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>176054; 189267</t>
+          <t>177621; 189410</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>204477; 221803</t>
+          <t>204959; 221800</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>308374; 327651</t>
+          <t>310524; 327662</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>229148; 245730</t>
+          <t>230874; 246724</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>211956; 232551</t>
+          <t>211828; 232570</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>357881; 378975</t>
+          <t>357019; 378427</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>252508; 277419</t>
+          <t>251671; 276348</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>424438; 450235</t>
+          <t>422381; 450163</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>674149; 701082</t>
+          <t>672469; 700634</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>487771; 517733</t>
+          <t>489827; 518529</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>54064; 61391</t>
+          <t>53936; 61372</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>119784; 132024</t>
+          <t>120374; 132071</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>115870; 129195</t>
+          <t>115309; 128383</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>170800; 183672</t>
+          <t>170573; 184156</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>308114; 331770</t>
+          <t>308306; 331054</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>211469; 232347</t>
+          <t>211698; 232469</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>229253; 243897</t>
+          <t>228662; 244120</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>434697; 460244</t>
+          <t>433642; 459958</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>333358; 357579</t>
+          <t>332907; 356722</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8266; 10172</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3504; 8182</t>
+          <t>4110; 8182</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11504; 18389</t>
+          <t>11599; 18398</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>226996; 241818</t>
+          <t>226335; 241906</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>257688; 275463</t>
+          <t>257927; 274802</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>171163; 186353</t>
+          <t>170058; 185996</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>236926; 251968</t>
+          <t>237494; 252171</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>265023; 282224</t>
+          <t>264780; 282304</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>186361; 203397</t>
+          <t>185292; 202860</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>546033; 577409</t>
+          <t>542866; 575356</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>881615; 916099</t>
+          <t>880605; 917356</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>674031; 704440</t>
+          <t>673514; 705050</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>901943; 937550</t>
+          <t>901138; 936255</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1364314; 1408145</t>
+          <t>1360677; 1408242</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>946520; 992633</t>
+          <t>947391; 992137</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1458885; 1506410</t>
+          <t>1457538; 1505427</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2258936; 2314987</t>
+          <t>2257881; 2314212</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1635553; 1688284</t>
+          <t>1632447; 1686192</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$nadie-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P02E$nadie-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72,51; 87,25</t>
+          <t>73,53; 87,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78,87; 91,14</t>
+          <t>80,1; 91,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,42; 92,5</t>
+          <t>78,18; 92,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79,9; 92,78</t>
+          <t>80,13; 92,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,57; 93,33</t>
+          <t>82,8; 93,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,02; 89,19</t>
+          <t>76,73; 89,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,89; 88,47</t>
+          <t>78,89; 88,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>83,6; 91,39</t>
+          <t>83,02; 91,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79,6; 89,0</t>
+          <t>79,12; 88,74</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,17; 93,82</t>
+          <t>76,79; 93,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,17; 95,6</t>
+          <t>85,36; 95,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,49; 94,7</t>
+          <t>82,07; 94,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87,54; 96,36</t>
+          <t>87,34; 96,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,24; 96,54</t>
+          <t>89,67; 96,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,97; 88,76</t>
+          <t>76,25; 88,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,1; 93,79</t>
+          <t>85,52; 93,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>88,92; 95,16</t>
+          <t>89,22; 95,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81,0; 89,91</t>
+          <t>81,17; 90,14</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86,7; 95,72</t>
+          <t>86,49; 96,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,6; 93,16</t>
+          <t>84,74; 93,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,81; 97,16</t>
+          <t>89,04; 97,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77,84; 94,03</t>
+          <t>77,17; 93,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>81,73; 94,56</t>
+          <t>80,78; 94,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,09; 100,0</t>
+          <t>89,45; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,56; 94,24</t>
+          <t>85,97; 94,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85,53; 92,52</t>
+          <t>85,2; 92,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91,36; 97,42</t>
+          <t>91,2; 97,54</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87,7; 94,9</t>
+          <t>87,84; 94,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90,91; 95,93</t>
+          <t>90,82; 96,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90,15; 96,34</t>
+          <t>89,46; 96,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84,96; 93,28</t>
+          <t>84,29; 92,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,57; 94,94</t>
+          <t>89,2; 94,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,41; 89,4</t>
+          <t>81,21; 89,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,44; 93,19</t>
+          <t>87,52; 92,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>90,86; 94,66</t>
+          <t>90,85; 94,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,66; 91,74</t>
+          <t>86,36; 91,67</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,49; 98,41</t>
+          <t>86,62; 98,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88,97; 97,62</t>
+          <t>88,87; 97,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84,76; 94,37</t>
+          <t>85,16; 94,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89,95; 97,11</t>
+          <t>90,51; 97,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,19; 92,55</t>
+          <t>86,54; 92,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,86; 93,18</t>
+          <t>85,43; 93,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,74; 96,88</t>
+          <t>90,44; 96,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>87,96; 93,3</t>
+          <t>88,42; 93,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>86,35; 92,53</t>
+          <t>86,76; 92,74</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1233,42 +1233,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50,23; 100,0</t>
+          <t>48,9; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59,97; 95,12</t>
+          <t>61,35; 95,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>90,71; 96,95</t>
+          <t>90,67; 96,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>90,02; 95,91</t>
+          <t>90,32; 95,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87,47; 95,66</t>
+          <t>87,57; 95,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>91,45; 97,1</t>
+          <t>91,39; 97,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>89,85; 95,79</t>
+          <t>89,91; 95,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>86,68; 94,9</t>
+          <t>86,87; 94,79</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>86,69; 91,88</t>
+          <t>87,12; 92,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>89,42; 93,15</t>
+          <t>89,47; 93,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89,14; 93,32</t>
+          <t>89,1; 93,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89,69; 93,18</t>
+          <t>89,74; 93,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>89,88; 93,02</t>
+          <t>90,08; 92,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,53; 89,57</t>
+          <t>85,63; 89,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,37; 92,3</t>
+          <t>89,39; 92,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>90,36; 92,62</t>
+          <t>90,31; 92,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>87,62; 90,5</t>
+          <t>87,59; 90,59</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>82714; 99535</t>
+          <t>83882; 99857</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>118961; 137464</t>
+          <t>120820; 138248</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75953; 89594</t>
+          <t>75727; 89642</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84828; 98510</t>
+          <t>85080; 98462</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>136805; 152785</t>
+          <t>135536; 153034</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>110008; 127387</t>
+          <t>109591; 127712</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>173759; 194853</t>
+          <t>173746; 195009</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>262946; 287451</t>
+          <t>261132; 287178</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>190792; 213324</t>
+          <t>189632; 212691</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64062; 79948</t>
+          <t>65444; 79432</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>131593; 147720</t>
+          <t>131885; 147917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89466; 101479</t>
+          <t>87947; 101247</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>124922; 137508</t>
+          <t>124633; 137378</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>176639; 191085</t>
+          <t>177484; 191188</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>119543; 139664</t>
+          <t>119983; 139934</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>193957; 213766</t>
+          <t>194922; 214226</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>313399; 335368</t>
+          <t>314438; 335716</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>214266; 237821</t>
+          <t>214710; 238445</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>104607; 115495</t>
+          <t>104357; 115905</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>164455; 181109</t>
+          <t>164733; 181311</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>124362; 136049</t>
+          <t>124679; 136075</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52445; 63354</t>
+          <t>51999; 63267</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>89404; 103433</t>
+          <t>88365; 103235</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48458; 54394</t>
+          <t>48656; 54394</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>160884; 177197</t>
+          <t>161654; 177027</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>259832; 281060</t>
+          <t>258816; 281313</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>177621; 189410</t>
+          <t>177313; 189641</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>204959; 221800</t>
+          <t>205281; 221770</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>310524; 327662</t>
+          <t>310226; 327970</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>230874; 246724</t>
+          <t>229123; 246358</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>211828; 232570</t>
+          <t>210159; 231401</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>357019; 378427</t>
+          <t>355526; 378139</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>251671; 276348</t>
+          <t>251031; 276064</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>422381; 450163</t>
+          <t>422738; 449146</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>672469; 700634</t>
+          <t>672450; 700623</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>489827; 518529</t>
+          <t>488119; 518170</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>53936; 61372</t>
+          <t>54020; 61377</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>120374; 132071</t>
+          <t>120238; 132015</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>115309; 128383</t>
+          <t>115850; 129193</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>170573; 184156</t>
+          <t>171628; 184428</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>308306; 331054</t>
+          <t>309569; 331793</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>211698; 232469</t>
+          <t>213139; 232308</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>228662; 244120</t>
+          <t>227893; 243770</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>433642; 459958</t>
+          <t>435929; 461022</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>332907; 356722</t>
+          <t>334468; 357524</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2459,42 +2459,42 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4110; 8182</t>
+          <t>4001; 8182</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11599; 18398</t>
+          <t>11868; 18407</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>226335; 241906</t>
+          <t>226237; 241632</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>257927; 274802</t>
+          <t>258780; 274927</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>170058; 185996</t>
+          <t>170257; 185680</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>237494; 252171</t>
+          <t>237349; 252289</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>264780; 282304</t>
+          <t>264966; 282267</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>185292; 202860</t>
+          <t>185702; 202624</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>542866; 575356</t>
+          <t>545566; 576200</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>880605; 917356</t>
+          <t>881128; 917470</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>673514; 705050</t>
+          <t>673150; 704930</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>901138; 936255</t>
+          <t>901659; 938674</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1360677; 1408242</t>
+          <t>1363701; 1407693</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>947391; 992137</t>
+          <t>948391; 993099</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1457538; 1505427</t>
+          <t>1457970; 1504774</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2257881; 2314212</t>
+          <t>2256582; 2313820</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1632447; 1686192</t>
+          <t>1631935; 1687808</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$nadie-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P02E$nadie-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
+          <t>Población que no tiene ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
+          <t>Población que no tiene ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
